--- a/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)_7_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)_7_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)_7_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)_7_CALIFICADO.xlsx
@@ -5902,9 +5902,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -6151,9 +6151,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6657,9 +6657,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -7163,9 +7163,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -7416,9 +7416,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -7669,9 +7669,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -8681,9 +8681,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -8934,9 +8934,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -9187,9 +9187,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -9440,9 +9440,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)_7_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)_7_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4333,11 +4277,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -4345,7 +4285,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4586,11 +4526,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -4598,7 +4534,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4839,11 +4775,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -4851,7 +4783,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5092,11 +5024,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -5104,7 +5032,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5345,11 +5273,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -5357,7 +5281,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5598,11 +5522,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -5610,7 +5530,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5851,11 +5771,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -5863,7 +5779,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6100,11 +6016,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -6112,7 +6024,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6353,11 +6265,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -6365,7 +6273,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6606,11 +6514,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -6618,7 +6522,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6859,11 +6763,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -6871,7 +6771,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7112,11 +7012,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -7124,7 +7020,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7365,11 +7261,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -7377,7 +7269,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7618,11 +7510,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -7630,7 +7518,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7871,11 +7759,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -7883,7 +7767,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8124,11 +8008,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -8136,7 +8016,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8377,11 +8257,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -8389,7 +8265,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8630,11 +8506,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -8642,7 +8514,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8883,11 +8755,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -8895,7 +8763,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9136,11 +9004,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -9148,7 +9012,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9389,11 +9253,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -9401,7 +9261,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9642,11 +9502,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -9654,7 +9510,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9895,11 +9751,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -9907,7 +9759,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10148,11 +10000,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -10160,7 +10008,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10401,11 +10249,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -10413,7 +10257,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10654,11 +10498,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800392</t>
@@ -10666,7 +10506,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED)</t>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
